--- a/Scripts/ProjectWise/ExecucaoManualUsuario/Modelo_Criacao_Usuarios_ProjectWise.xlsx
+++ b/Scripts/ProjectWise/ExecucaoManualUsuario/Modelo_Criacao_Usuarios_ProjectWise.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b5e890b22f75f267/Desktop/Scritps_novos/Scripts/ProjectWise/ExecucaoManualUsuario/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupoecorodovias-my.sharepoint.com/personal/t_peterson_caputti_ecorodovias_com_br/Documents/Área de Trabalho/Scritps_novos/Scripts/ProjectWise/ExecucaoManualUsuario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="37" documentId="11_DAC49202D5916362E57A22667785202811083D4B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C7B95C8-5A41-4B04-A03C-EEB5E2B0ED26}"/>
+  <xr:revisionPtr revIDLastSave="51" documentId="11_DAC49202D5916362E57A22667785202811083D4B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{504F88FF-4101-4152-BBDE-39C6AE956DB8}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="12">
   <si>
     <t>Name</t>
   </si>
@@ -44,20 +44,38 @@
     <t>E-mail</t>
   </si>
   <si>
-    <t xml:space="preserve"> Jessica Mello</t>
-  </si>
-  <si>
-    <t>Jessica.mello@egis-group.com</t>
-  </si>
-  <si>
-    <t>Projetista e consulta a todas as revisões</t>
+    <t>Fabrizia Oliverii</t>
+  </si>
+  <si>
+    <t>fabrizia.oliverii@jgpconsultoria.com.br</t>
+  </si>
+  <si>
+    <t>Luís Eduardo G. Almeida</t>
+  </si>
+  <si>
+    <t>luis.almeida@jgpconsultoria.com.br</t>
+  </si>
+  <si>
+    <t>Marcos Peixoto</t>
+  </si>
+  <si>
+    <t>marcos.peixoto@jgpconsultoria.com.br</t>
+  </si>
+  <si>
+    <t>Marlon Rocha</t>
+  </si>
+  <si>
+    <t>marlon.rocha@jgpconsultoria.com.br</t>
+  </si>
+  <si>
+    <t>Engenharia consulta ultima revisão</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -69,6 +87,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -88,14 +112,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Hiperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{89BCDF74-85A0-4A44-AA54-03B6F83ACE36}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
@@ -110,10 +137,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -433,11 +456,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="48.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -457,13 +480,49 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
       </c>
     </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C3" r:id="rId1" xr:uid="{AA8684BD-8A75-4319-857E-60776020F67A}"/>
+  </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/Scripts/ProjectWise/ExecucaoManualUsuario/Modelo_Criacao_Usuarios_ProjectWise.xlsx
+++ b/Scripts/ProjectWise/ExecucaoManualUsuario/Modelo_Criacao_Usuarios_ProjectWise.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupoecorodovias-my.sharepoint.com/personal/t_peterson_caputti_ecorodovias_com_br/Documents/Área de Trabalho/Scritps_novos/Scripts/ProjectWise/ExecucaoManualUsuario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="51" documentId="11_DAC49202D5916362E57A22667785202811083D4B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{504F88FF-4101-4152-BBDE-39C6AE956DB8}"/>
+  <xr:revisionPtr revIDLastSave="53" documentId="11_DAC49202D5916362E57A22667785202811083D4B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E35A183E-60B4-47D2-8722-7A1D23185DBB}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Usuarios" sheetId="1" r:id="rId1"/>
@@ -137,6 +137,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Scripts/ProjectWise/ExecucaoManualUsuario/Modelo_Criacao_Usuarios_ProjectWise.xlsx
+++ b/Scripts/ProjectWise/ExecucaoManualUsuario/Modelo_Criacao_Usuarios_ProjectWise.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupoecorodovias-my.sharepoint.com/personal/t_peterson_caputti_ecorodovias_com_br/Documents/Área de Trabalho/Scritps_novos/Scripts/ProjectWise/ExecucaoManualUsuario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="53" documentId="11_DAC49202D5916362E57A22667785202811083D4B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E35A183E-60B4-47D2-8722-7A1D23185DBB}"/>
+  <xr:revisionPtr revIDLastSave="93" documentId="11_DAC49202D5916362E57A22667785202811083D4B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F458512A-D48B-4C6F-97C3-613D136B7584}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Usuarios" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="48">
   <si>
     <t>Name</t>
   </si>
@@ -44,38 +44,147 @@
     <t>E-mail</t>
   </si>
   <si>
-    <t>Fabrizia Oliverii</t>
-  </si>
-  <si>
-    <t>fabrizia.oliverii@jgpconsultoria.com.br</t>
-  </si>
-  <si>
-    <t>Luís Eduardo G. Almeida</t>
-  </si>
-  <si>
-    <t>luis.almeida@jgpconsultoria.com.br</t>
-  </si>
-  <si>
-    <t>Marcos Peixoto</t>
-  </si>
-  <si>
-    <t>marcos.peixoto@jgpconsultoria.com.br</t>
-  </si>
-  <si>
-    <t>Marlon Rocha</t>
-  </si>
-  <si>
-    <t>marlon.rocha@jgpconsultoria.com.br</t>
-  </si>
-  <si>
-    <t>Engenharia consulta ultima revisão</t>
+    <t>Wesley Mezine</t>
+  </si>
+  <si>
+    <t>Leonardo Botelho</t>
+  </si>
+  <si>
+    <t>Bruna Rocha</t>
+  </si>
+  <si>
+    <t>Letícia Silva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+José Milton</t>
+  </si>
+  <si>
+    <t>Daniele Spitz</t>
+  </si>
+  <si>
+    <t>João Paulo</t>
+  </si>
+  <si>
+    <t>Aline Santos</t>
+  </si>
+  <si>
+    <t>Cláudia Campos</t>
+  </si>
+  <si>
+    <t>Matheus Santos</t>
+  </si>
+  <si>
+    <t>Vinicius Viana</t>
+  </si>
+  <si>
+    <t>Samara Capitol</t>
+  </si>
+  <si>
+    <t>Larissa Macedo</t>
+  </si>
+  <si>
+    <t>Fernanda Santos</t>
+  </si>
+  <si>
+    <t>Luciano Moura</t>
+  </si>
+  <si>
+    <t>Andressa Reis</t>
+  </si>
+  <si>
+    <t>Raíssa Farias</t>
+  </si>
+  <si>
+    <t>Patrícia Hidalgo</t>
+  </si>
+  <si>
+    <t>Ronaldo Silva</t>
+  </si>
+  <si>
+    <t>Célio Araujo</t>
+  </si>
+  <si>
+    <t>Hermes Vinicius</t>
+  </si>
+  <si>
+    <t>wesley.mezine@egis-group.com</t>
+  </si>
+  <si>
+    <t>leonardo.botelho@egis-group.com</t>
+  </si>
+  <si>
+    <t>bruna.rocha@egis-group.com</t>
+  </si>
+  <si>
+    <t>leticia.silva@egis-group.com</t>
+  </si>
+  <si>
+    <t>Daniele.spitz@egis-group.com</t>
+  </si>
+  <si>
+    <t>jose.junior@egis-group.com</t>
+  </si>
+  <si>
+    <t>joao.carvalho@egis-group.com</t>
+  </si>
+  <si>
+    <t>aline.baldo@egis-group.com</t>
+  </si>
+  <si>
+    <t>claudia.campos@egis-group.com</t>
+  </si>
+  <si>
+    <t>matheus.santos@egis-group.com</t>
+  </si>
+  <si>
+    <t>vinicius.silva@egis-group.com</t>
+  </si>
+  <si>
+    <t>samara.silva@egis-group.com</t>
+  </si>
+  <si>
+    <t>pietro.sa@egis-group.com</t>
+  </si>
+  <si>
+    <t>Pietro As</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> larissa.macedo@egis-group.com</t>
+  </si>
+  <si>
+    <t>fernanda.santos@egis-group.com</t>
+  </si>
+  <si>
+    <t>luciano.moura@egis-group.com</t>
+  </si>
+  <si>
+    <t>andressa.reis@egis-group.com</t>
+  </si>
+  <si>
+    <t>raissa.farias@egis-group.com</t>
+  </si>
+  <si>
+    <t>patricia.hidalgo@egis-group.com</t>
+  </si>
+  <si>
+    <t>ronaldo.silva@egis-group.com</t>
+  </si>
+  <si>
+    <t>celio.araujo@egis-group.com</t>
+  </si>
+  <si>
+    <t>hermes.almeida@egis-group.com</t>
+  </si>
+  <si>
+    <t>Projetista e consulta a todas as revisões</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -93,6 +202,23 @@
       <sz val="11"/>
       <color theme="10"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -117,9 +243,20 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hiperlink" xfId="2" builtinId="8"/>
@@ -460,7 +597,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.77734375" bestFit="1" customWidth="1"/>
@@ -480,52 +617,271 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" t="s">
-        <v>10</v>
-      </c>
+      <c r="B10" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C13" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C20" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C22" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C23" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="3"/>
+      <c r="B24" s="3"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="3"/>
+      <c r="B25" s="3"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="3"/>
+      <c r="B26" s="3"/>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C3" r:id="rId1" xr:uid="{AA8684BD-8A75-4319-857E-60776020F67A}"/>
+    <hyperlink ref="C6" r:id="rId1" xr:uid="{E7FAC924-0CEC-46A8-A635-1B660E8CA2AA}"/>
+    <hyperlink ref="C7" r:id="rId2" xr:uid="{E1FF300B-1540-4D8A-BCBB-A38250ADBA11}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
